--- a/output/pdf_financials_xlsx/FSY.xlsx
+++ b/output/pdf_financials_xlsx/FSY.xlsx
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-1.656775</v>
+        <v>-16.113169</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-2.452278</v>
+        <v>-12.082112</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>2.452278</v>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>7.228197</v>
+        <v>-7.228197</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4.814917</v>
+        <v>-4.814917</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-5.295453</v>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>7.228197</v>
+        <v>-7.228197</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>4.814917</v>
+        <v>-4.814917</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-5.295453</v>
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>80.3133</v>
+        <v>-80.3133</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>80.248617</v>
+        <v>-80.248617</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>75.64932899999999</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>18.64693552213783</v>
+        <v>181.3530644778622</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>33.74449151288771</v>
+        <v>166.2555084871123</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>33.74449151288771</v>
@@ -44996,7 +44996,7 @@
         </is>
       </c>
       <c r="G541" s="5" t="n">
-        <v>4.814917</v>
+        <v>-4.814917</v>
       </c>
       <c r="H541" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         </is>
       </c>
       <c r="G544" s="5" t="n">
-        <v>4.814917</v>
+        <v>-4.814917</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
@@ -47483,10 +47483,10 @@
         </is>
       </c>
       <c r="E576" s="5" t="n">
-        <v>7.228197</v>
+        <v>-7.228197</v>
       </c>
       <c r="F576" s="5" t="n">
-        <v>4.814917</v>
+        <v>-4.814917</v>
       </c>
       <c r="G576" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FSY.xlsx
+++ b/output/pdf_financials_xlsx/FSY.xlsx
@@ -919,10 +919,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.145146</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.119171</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001266</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00515</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
         <v>7.267195</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>7.267195</v>
+        <v>7.122049</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-5.319337</v>
+        <v>-5.438508</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1709,10 +1709,10 @@
         <v>-6.136588</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-74.880033</v>
+        <v>-74.878767</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.365708</v>
+        <v>-0.360558</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
         <v>7.267195</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>7.482728</v>
+        <v>7.337582</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.209627</v>
+        <v>-5.328798</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1799,10 +1799,10 @@
         <v>-6.116543</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-74.87877899999999</v>
+        <v>-74.87751299999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.365574</v>
+        <v>-0.360424</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -43167,7 +43167,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -44173,7 +44173,7 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
